--- a/src/nodes/LPC/compressor_stage_3_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/LPC/compressor_stage_3_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.001781123102526175</v>
       </c>
       <c r="B2">
-        <v>0.0011913691232231557</v>
+        <v>0.0013231722328100925</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.00356224620505235</v>
       </c>
       <c r="B3">
-        <v>0.0019435401751825604</v>
+        <v>0.00212521473164023</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0053433693075785249</v>
       </c>
       <c r="B4">
-        <v>0.0026095549274973919</v>
+        <v>0.0028297017429696272</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0071244924101047</v>
       </c>
       <c r="B5">
-        <v>0.00320935720718693</v>
+        <v>0.00346049556464312</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0089056155126308739</v>
       </c>
       <c r="B6">
-        <v>0.0037512553258206589</v>
+        <v>0.0040275008960139981</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.01068673861515705</v>
       </c>
       <c r="B7">
-        <v>0.004240096971470866</v>
+        <v>0.0045364758557312219</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.012467861717683224</v>
       </c>
       <c r="B8">
-        <v>0.0046788356031929245</v>
+        <v>0.0049909084573543372</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0142489848202094</v>
       </c>
       <c r="B9">
-        <v>0.00507190469954961</v>
+        <v>0.0053960691042093745</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.016030107922735574</v>
       </c>
       <c r="B10">
-        <v>0.005424057199585536</v>
+        <v>0.0057576145501483881</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.017811231025261748</v>
       </c>
       <c r="B11">
-        <v>0.0057398438647652626</v>
+        <v>0.0060809645613610751</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.019592354127787925</v>
       </c>
       <c r="B12">
-        <v>0.0060217733519668491</v>
+        <v>0.0063690910898270871</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0213734772303141</v>
       </c>
       <c r="B13">
-        <v>0.0062643880773024154</v>
+        <v>0.0066154118183482736</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.023154600332840274</v>
       </c>
       <c r="B14">
-        <v>0.0064644755407868154</v>
+        <v>0.0068160411657556376</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.024935723435366448</v>
       </c>
       <c r="B15">
-        <v>0.00663576981881179</v>
+        <v>0.0069874347641745577</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.026716846537892622</v>
       </c>
       <c r="B16">
-        <v>0.0067908670957758889</v>
+        <v>0.0071446849961027984</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.0284979696404188</v>
       </c>
       <c r="B17">
-        <v>0.0069208654117280119</v>
+        <v>0.0072770900322332473</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.030279092742944973</v>
       </c>
       <c r="B18">
-        <v>0.0070142284538768831</v>
+        <v>0.007370789617497292</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.032060215845471148</v>
       </c>
       <c r="B19">
-        <v>0.007070380642420159</v>
+        <v>0.0074250840055851844</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.033841338947997325</v>
       </c>
       <c r="B20">
-        <v>0.0070914865808027307</v>
+        <v>0.0074425635773768886</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.035622462050523496</v>
       </c>
       <c r="B21">
-        <v>0.00707971087246949</v>
+        <v>0.0074258187137523756</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.037403585153049673</v>
       </c>
       <c r="B22">
-        <v>0.00703682762762486</v>
+        <v>0.0073769735378361647</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.039184708255575851</v>
       </c>
       <c r="B23">
-        <v>0.0069630489835113716</v>
+        <v>0.0072962871417309944</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.040965831358102021</v>
       </c>
       <c r="B24">
-        <v>0.0068581965841310938</v>
+        <v>0.0071835523597841558</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.0427469544606282</v>
       </c>
       <c r="B25">
-        <v>0.0067220920734860912</v>
+        <v>0.0070385620263429408</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.04452807756315437</v>
       </c>
       <c r="B26">
-        <v>0.0065544833660963085</v>
+        <v>0.0068610228006724333</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.046309200665680547</v>
       </c>
       <c r="B27">
-        <v>0.0063548234585532075</v>
+        <v>0.0066502966417088692</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.048090323768206725</v>
       </c>
       <c r="B28">
-        <v>0.0061224916179661313</v>
+        <v>0.0064056593333062769</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.049871446870732895</v>
       </c>
       <c r="B29">
-        <v>0.0058568671114444248</v>
+        <v>0.0061263866593186857</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.051652569973259073</v>
       </c>
       <c r="B30">
-        <v>0.005557599441667626</v>
+        <v>0.0058120811675654305</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.053433693075785244</v>
       </c>
       <c r="B31">
-        <v>0.0052254190535960619</v>
+        <v>0.0054636524617270909</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.055214816178311421</v>
       </c>
       <c r="B32">
-        <v>0.0048613266277602483</v>
+        <v>0.00508233690944955</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.0569959392808376</v>
       </c>
       <c r="B33">
-        <v>0.0044663228446907106</v>
+        <v>0.0046693708783786944</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.058777062383363769</v>
       </c>
       <c r="B34">
-        <v>0.0040409377046950025</v>
+        <v>0.0042254288401703827</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.060558185485889947</v>
       </c>
       <c r="B35">
-        <v>0.0035838184871888239</v>
+        <v>0.0037489376825203535</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.062339308588416117</v>
       </c>
       <c r="B36">
-        <v>0.0030931417913649104</v>
+        <v>0.0032377623971343215</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.0641204316909423</v>
       </c>
       <c r="B37">
-        <v>0.0025670842164159909</v>
+        <v>0.0026897679757179943</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.065901554793468473</v>
       </c>
       <c r="B38">
-        <v>0.0020026883442031624</v>
+        <v>0.0021014616167917104</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.06768267789599465</v>
       </c>
       <c r="B39">
-        <v>0.0013924606872609594</v>
+        <v>0.0014639193461343093</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.069463800998520828</v>
       </c>
       <c r="B40">
-        <v>0.00072777374079227748</v>
+        <v>0.00076685939633925509</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.069463800998520828</v>
       </c>
       <c r="B43">
-        <v>0.00033691718532250138</v>
+        <v>0.00029783152977552388</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.06768267789599465</v>
       </c>
       <c r="B44">
-        <v>0.00067787409852745927</v>
+        <v>0.00060641543965410936</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.065901554793468473</v>
       </c>
       <c r="B45">
-        <v>0.0010149556183176817</v>
+        <v>0.00091618234572913356</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.0641204316909423</v>
       </c>
       <c r="B46">
-        <v>0.001340246623395962</v>
+        <v>0.0012175628640939589</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.062339308588416117</v>
       </c>
       <c r="B47">
-        <v>0.0016469357336708023</v>
+        <v>0.0015023151279013912</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.060558185485889947</v>
       </c>
       <c r="B48">
-        <v>0.0019326265338735368</v>
+        <v>0.0017675073385420078</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.058777062383363769</v>
       </c>
       <c r="B49">
-        <v>0.0021960263499412121</v>
+        <v>0.0020115352144658332</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.0569959392808376</v>
       </c>
       <c r="B50">
-        <v>0.0024358425078108712</v>
+        <v>0.002232794474122887</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.055214816178311421</v>
       </c>
       <c r="B51">
-        <v>0.0026512238108672391</v>
+        <v>0.0024302135291779377</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.053433693075785244</v>
       </c>
       <c r="B52">
-        <v>0.002843084972285765</v>
+        <v>0.0026048515641547356</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.051652569973259073</v>
       </c>
       <c r="B53">
-        <v>0.0030127821826895804</v>
+        <v>0.0027583004567917763</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.049871446870732895</v>
       </c>
       <c r="B54">
-        <v>0.0031616716327018176</v>
+        <v>0.0028921520848275576</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.048090323768206725</v>
       </c>
       <c r="B55">
-        <v>0.0032908144645646697</v>
+        <v>0.0030076467492245237</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.046309200665680547</v>
       </c>
       <c r="B56">
-        <v>0.0034000916269965784</v>
+        <v>0.0031046184438409158</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.04452807756315437</v>
       </c>
       <c r="B57">
-        <v>0.0034890890203350482</v>
+        <v>0.0031825495857589229</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.0427469544606282</v>
       </c>
       <c r="B58">
-        <v>0.0035573925449175836</v>
+        <v>0.0032409225920607336</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.040965831358102021</v>
       </c>
       <c r="B59">
-        <v>0.0036046388276004737</v>
+        <v>0.0032792830519474121</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.039184708255575851</v>
       </c>
       <c r="B60">
-        <v>0.00363066740131514</v>
+        <v>0.0032974292430955174</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.037403585153049673</v>
       </c>
       <c r="B61">
-        <v>0.003635368525511789</v>
+        <v>0.0032952226153004829</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.035622462050523496</v>
       </c>
       <c r="B62">
-        <v>0.0036186324596406273</v>
+        <v>0.0032725246183577415</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.033841338947997325</v>
       </c>
       <c r="B63">
-        <v>0.0035807166150611373</v>
+        <v>0.0032296396184869776</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.032060215845471148</v>
       </c>
       <c r="B64">
-        <v>0.0035233470107699045</v>
+        <v>0.0031686436476048791</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.030279092742944973</v>
       </c>
       <c r="B65">
-        <v>0.0034486168176727926</v>
+        <v>0.0030920556540523832</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.0284979696404188</v>
       </c>
       <c r="B66">
-        <v>0.0033586192066756629</v>
+        <v>0.003002394586170428</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.026716846537892622</v>
       </c>
       <c r="B67">
-        <v>0.0032526880925067923</v>
+        <v>0.0028988701921798831</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.024935723435366448</v>
       </c>
       <c r="B68">
-        <v>0.00311912036518411</v>
+        <v>0.0027674554198213424</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.023154600332840274</v>
       </c>
       <c r="B69">
-        <v>0.0029488192910986006</v>
+        <v>0.00259725366612978</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0213734772303141</v>
       </c>
       <c r="B70">
-        <v>0.0027541506668438296</v>
+        <v>0.0024031269257979715</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.019592354127787925</v>
       </c>
       <c r="B71">
-        <v>0.0025485959733644783</v>
+        <v>0.0022012782355042416</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.017811231025261748</v>
       </c>
       <c r="B72">
-        <v>0.0023286368988071318</v>
+        <v>0.0019875162022113192</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.016030107922735574</v>
       </c>
       <c r="B73">
-        <v>0.0020884836939570103</v>
+        <v>0.0017549263433941577</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0142489848202094</v>
       </c>
       <c r="B74">
-        <v>0.0018302606529519716</v>
+        <v>0.0015060962482922079</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.012467861717683224</v>
       </c>
       <c r="B75">
-        <v>0.0015581070615787972</v>
+        <v>0.0012460342074173843</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.01068673861515705</v>
       </c>
       <c r="B76">
-        <v>0.0012763081288673108</v>
+        <v>0.00097992924460695539</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0089056155126308739</v>
       </c>
       <c r="B77">
-        <v>0.00098879962388725832</v>
+        <v>0.00071255405369391835</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0071244924101047</v>
       </c>
       <c r="B78">
-        <v>0.00069797363262502339</v>
+        <v>0.000446835275168833</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0053433693075785249</v>
       </c>
       <c r="B79">
-        <v>0.00040808677277503959</v>
+        <v>0.00018793995730280458</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.00356224620505235</v>
       </c>
       <c r="B80">
-        <v>0.00012679461060586251</v>
+        <v>-5.48799458518072E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.001781123102526175</v>
       </c>
       <c r="B81">
-        <v>-0.00012666197264621373</v>
+        <v>-0.00025846508223315061</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0019287221571817716</v>
       </c>
       <c r="B2">
-        <v>0.001593993498114697</v>
+        <v>0.0018794443773775989</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0038574443143635432</v>
       </c>
       <c r="B3">
-        <v>0.0025337656143435082</v>
+        <v>0.0029272249344085895</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0057861664715453155</v>
       </c>
       <c r="B4">
-        <v>0.0033544114526859576</v>
+        <v>0.0038311915699412911</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0077148886287270865</v>
       </c>
       <c r="B5">
-        <v>0.0040860527286178776</v>
+        <v>0.0046299523769431361</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0096436107859088575</v>
       </c>
       <c r="B6">
-        <v>0.0047411791683672063</v>
+        <v>0.00533945443783009</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.011572332943090631</v>
       </c>
       <c r="B7">
-        <v>0.0053270436432483036</v>
+        <v>0.0059689223771583963</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.013501055100272401</v>
       </c>
       <c r="B8">
-        <v>0.0058480319686978295</v>
+        <v>0.0065238997148658424</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.015429777257454173</v>
       </c>
       <c r="B9">
-        <v>0.0063107836820319521</v>
+        <v>0.0070128385472461169</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.017358499414635943</v>
       </c>
       <c r="B10">
-        <v>0.0067224273739381404</v>
+        <v>0.0074448248902119676</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.019287221571817715</v>
       </c>
       <c r="B11">
-        <v>0.0070897941267095959</v>
+        <v>0.0078285718617965017</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.021215943728999487</v>
       </c>
       <c r="B12">
-        <v>0.0074166235228124216</v>
+        <v>0.0081688224198377835</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.023144665886181262</v>
       </c>
       <c r="B13">
-        <v>0.0076945866537985819</v>
+        <v>0.00845481177927335</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.02507338804336303</v>
       </c>
       <c r="B14">
-        <v>0.0079187624943232483</v>
+        <v>0.0086801611978930462</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.027002110200544802</v>
       </c>
       <c r="B15">
-        <v>0.0081099300423685561</v>
+        <v>0.0088715438477964953</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.028930832357726574</v>
       </c>
       <c r="B16">
-        <v>0.0082871468888345585</v>
+        <v>0.0090534234286202327</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.030859554514908346</v>
       </c>
       <c r="B17">
-        <v>0.0084368849729659912</v>
+        <v>0.0092083738358387</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.032788276672090118</v>
       </c>
       <c r="B18">
-        <v>0.0085416271673996458</v>
+        <v>0.0093138448941697035</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.034716998829271886</v>
       </c>
       <c r="B19">
-        <v>0.0086004857299958049</v>
+        <v>0.00936867994946663</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.036645720986453661</v>
       </c>
       <c r="B20">
-        <v>0.0086167302649206232</v>
+        <v>0.0093770707278667646</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.03857444314363543</v>
       </c>
       <c r="B21">
-        <v>0.0085936303763402624</v>
+        <v>0.0093432089555073854</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.040503165300817205</v>
       </c>
       <c r="B22">
-        <v>0.0085338675864339662</v>
+        <v>0.0092705341905208322</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.042431887457998974</v>
       </c>
       <c r="B23">
-        <v>0.0084377710894333463</v>
+        <v>0.009159477319019671</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.044360609615180749</v>
       </c>
       <c r="B24">
-        <v>0.0083050819975830931</v>
+        <v>0.0090097170591115269</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.046289331772362524</v>
       </c>
       <c r="B25">
-        <v>0.0081355414231279091</v>
+        <v>0.0088209321289040247</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.048218053929544286</v>
       </c>
       <c r="B26">
-        <v>0.007928782538129028</v>
+        <v>0.0085926663524239551</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.050146776086726061</v>
       </c>
       <c r="B27">
-        <v>0.0076840067539138248</v>
+        <v>0.008323923977374777</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.052075498243907836</v>
       </c>
       <c r="B28">
-        <v>0.0074003075416262162</v>
+        <v>0.00801357435737912</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.054004220401089605</v>
       </c>
       <c r="B29">
-        <v>0.0070767783724101163</v>
+        <v>0.0076604868460596054</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.05593294255827138</v>
       </c>
       <c r="B30">
-        <v>0.00671292647344185</v>
+        <v>0.0072640669787116035</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.057861664715453148</v>
       </c>
       <c r="B31">
-        <v>0.0063099140960273942</v>
+        <v>0.0068258650173214407</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.059790386872634917</v>
       </c>
       <c r="B32">
-        <v>0.0058693172475051247</v>
+        <v>0.0063479674055481744</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.061719109029816692</v>
       </c>
       <c r="B33">
-        <v>0.005392711935213429</v>
+        <v>0.0058324605870508734</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.06364783118699846</v>
       </c>
       <c r="B34">
-        <v>0.0048809652671104719</v>
+        <v>0.0052805245567410543</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.065576553344180236</v>
       </c>
       <c r="B35">
-        <v>0.0043321087536335613</v>
+        <v>0.0046897135145400459</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.067505275501362</v>
       </c>
       <c r="B36">
-        <v>0.0037434650058397866</v>
+        <v>0.0040566752116216326</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.069433997658543772</v>
       </c>
       <c r="B37">
-        <v>0.0031123566347862324</v>
+        <v>0.0033780573991595928</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.071362719815725548</v>
       </c>
       <c r="B38">
-        <v>0.0024343917337313033</v>
+        <v>0.0026483086708691032</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.073291441972907323</v>
       </c>
       <c r="B39">
-        <v>0.0016983203247386489</v>
+        <v>0.0018530809906309139</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.0752201641300891</v>
       </c>
       <c r="B40">
-        <v>0.00089117791207323134</v>
+        <v>0.00097582716486716914</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.07714888628727086</v>
       </c>
       <c r="B41">
-        <v>1.739815794443921E-17</v>
+        <v>1.7130493976063224E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.07714888628727086</v>
       </c>
       <c r="B42">
-        <v>1.7130493976063224E-17</v>
+        <v>1.7197409968157222E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.0752201641300891</v>
       </c>
       <c r="B43">
-        <v>0.00029863314251566813</v>
+        <v>0.00021398388972173037</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.073291441972907323</v>
       </c>
       <c r="B44">
-        <v>0.00061499566349279349</v>
+        <v>0.0004602349976005284</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.071362719815725548</v>
       </c>
       <c r="B45">
-        <v>0.00093697317376670254</v>
+        <v>0.00072305623662890269</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.069433997658543772</v>
       </c>
       <c r="B46">
-        <v>0.0012524512841727061</v>
+        <v>0.00098675051979934571</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.067505275501362</v>
       </c>
       <c r="B47">
-        <v>0.0015509935653668563</v>
+        <v>0.0012377833595850095</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.065576553344180236</v>
       </c>
       <c r="B48">
-        <v>0.0018288754272881686</v>
+        <v>0.0014712706663816844</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.06364783118699846</v>
       </c>
       <c r="B49">
-        <v>0.0020840502396964047</v>
+        <v>0.0016844909500658238</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.061719109029816692</v>
       </c>
       <c r="B50">
-        <v>0.0023144713723513215</v>
+        <v>0.0018747227205138774</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.059790386872634917</v>
       </c>
       <c r="B51">
-        <v>0.0025187661412037821</v>
+        <v>0.0020401159831607333</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.057861664715453148</v>
       </c>
       <c r="B52">
-        <v>0.0026982576469690702</v>
+        <v>0.0021823067256750242</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.05593294255827138</v>
       </c>
       <c r="B53">
-        <v>0.0028549429365535717</v>
+        <v>0.0023038024312838183</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.054004220401089605</v>
       </c>
       <c r="B54">
-        <v>0.0029908190568636766</v>
+        <v>0.0024071105832141858</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.052075498243907836</v>
       </c>
       <c r="B55">
-        <v>0.0031074398313558839</v>
+        <v>0.00249417301560298</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.050146776086726061</v>
       </c>
       <c r="B56">
-        <v>0.0032045861896871481</v>
+        <v>0.0025646689662261945</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.048218053929544286</v>
       </c>
       <c r="B57">
-        <v>0.0032815958380645349</v>
+        <v>0.0026177120237696073</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.046289331772362524</v>
       </c>
       <c r="B58">
-        <v>0.0033378064826951109</v>
+        <v>0.0026524157769189966</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.044360609615180749</v>
       </c>
       <c r="B59">
-        <v>0.003372636566884064</v>
+        <v>0.0026680015053556303</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.042431887457998974</v>
       </c>
       <c r="B60">
-        <v>0.0033858274823290661</v>
+        <v>0.0026641212527427406</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.040503165300817205</v>
       </c>
       <c r="B61">
-        <v>0.0033772013578259128</v>
+        <v>0.0026405347537390477</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.03857444314363543</v>
       </c>
       <c r="B62">
-        <v>0.0033465803221703959</v>
+        <v>0.0025970017430032724</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.036645720986453661</v>
       </c>
       <c r="B63">
-        <v>0.0032943470242976303</v>
+        <v>0.0025340065613514888</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.034716998829271886</v>
       </c>
       <c r="B64">
-        <v>0.0032231261937000068</v>
+        <v>0.0024549319742291796</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.032788276672090118</v>
       </c>
       <c r="B65">
-        <v>0.003136103080009237</v>
+        <v>0.0023638853532391788</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.030859554514908346</v>
       </c>
       <c r="B66">
-        <v>0.0030364629328570305</v>
+        <v>0.0022649740699843221</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.028930832357726574</v>
       </c>
       <c r="B67">
-        <v>0.0029232111103348283</v>
+        <v>0.0021569345705491532</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.027002110200544802</v>
       </c>
       <c r="B68">
-        <v>0.0027786334043729912</v>
+        <v>0.0020170195989450529</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.02507338804336303</v>
       </c>
       <c r="B69">
-        <v>0.002588971569334663</v>
+        <v>0.0018275728657648651</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.023144665886181262</v>
       </c>
       <c r="B70">
-        <v>0.0023730107754752132</v>
+        <v>0.0016127856500004465</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.021215943728999487</v>
       </c>
       <c r="B71">
-        <v>0.0021512312436348913</v>
+        <v>0.00139903234660953</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.019287221571817715</v>
       </c>
       <c r="B72">
-        <v>0.0019183499811012571</v>
+        <v>0.0011795722460143517</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.017358499414635943</v>
       </c>
       <c r="B73">
-        <v>0.0016656447600213468</v>
+        <v>0.00094324724374751927</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.015429777257454173</v>
       </c>
       <c r="B74">
-        <v>0.0013963996255327981</v>
+        <v>0.00069434476031863352</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.013501055100272401</v>
       </c>
       <c r="B75">
-        <v>0.0011169577455217379</v>
+        <v>0.00044108999935372508</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.011572332943090631</v>
       </c>
       <c r="B76">
-        <v>0.0008338925058776471</v>
+        <v>0.00019201377196755395</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0096436107859088575</v>
       </c>
       <c r="B77">
-        <v>0.000553252282127021</v>
+        <v>-4.5022987335862059E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0077148886287270865</v>
       </c>
       <c r="B78">
-        <v>0.00027875519034106121</v>
+        <v>-0.00026514445798419786</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0057861664715453155</v>
       </c>
       <c r="B79">
-        <v>1.6950631898619136E-05</v>
+        <v>-0.00045982948535671443</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0038574443143635432</v>
       </c>
       <c r="B80">
-        <v>-0.00022044962611206107</v>
+        <v>-0.0006139089461771422</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0019287221571817716</v>
       </c>
       <c r="B81">
-        <v>-0.00040416265672561856</v>
+        <v>-0.00068961353598852055</v>
       </c>
     </row>
     <row r="82" spans="1:2">
